--- a/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
+++ b/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.1-current</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
+++ b/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
+++ b/fhir/ihe.formatcode.fhir/ValueSet-formatcode.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
